--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-29 11:18</t>
+    <t xml:space="preserve">2026-08-19 14:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:19</t>
+    <t xml:space="preserve">2026-08-20 12:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 12:40</t>
+    <t xml:space="preserve">2026-08-28 15:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:07</t>
+    <t xml:space="preserve">2026-08-29 05:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -474,13 +474,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46.37</v>
+        <v>92.74</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>44.27</v>
+        <v>88.55</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2.1</v>
+        <v>4.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_intra_s_fonasa_a_2023_nuble.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:43</t>
+    <t xml:space="preserve">2026-09-07 11:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
